--- a/docs/springs_RH.xlsx
+++ b/docs/springs_RH.xlsx
@@ -136,7 +136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -204,8 +204,177 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,8 +411,168 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -251,12 +580,280 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -307,6 +904,102 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="10" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="18" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="right" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="13" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="15" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="23" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="right" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="17" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="18" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="29" fillId="26" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="right" wrapText="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="30" fillId="27" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="right" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="21" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="22" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="33" fillId="30" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="right" wrapText="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="34" fillId="31" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" horizontal="right" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="25" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="34" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="38" fillId="35" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="36" borderId="29" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="40" fillId="37" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="38" borderId="31" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="39" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+      <alignment vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -534,7 +1227,7 @@
     <col min="9" max="9" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23" customHeight="1">
+    <row r="1" spans="1:9" ht="12" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -545,33 +1238,35 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="32" customHeight="1">
+    <row r="2" spans="1:9" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="23" customHeight="1">
+    <row r="3" spans="1:9" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>黄色单元格为手动输入。</t>
+        </is>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="23" customHeight="1">
+    <row r="4" spans="1:9" ht="12" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -582,72 +1277,72 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="26" customHeight="1">
+    <row r="5" spans="1:9" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" ht="23" customHeight="1">
+    <row r="6" spans="1:9" ht="30" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="24" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="10">
+      <c r="G6" s="26"/>
+      <c r="H6" s="27">
         <v>2.5</v>
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" ht="23" customHeight="1">
+    <row r="7" spans="1:9" ht="29" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="29">
         <v>186</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="29">
         <v>188</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="11">
+      <c r="G7" s="31"/>
+      <c r="H7" s="32">
         <v>180</v>
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="23" customHeight="1">
+    <row r="8" spans="1:9" ht="29" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="34">
         <v>106</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="34">
         <v>108</v>
       </c>
       <c r="E8" s="1"/>
@@ -656,7 +1351,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" ht="23" customHeight="1">
+    <row r="9" spans="1:9" ht="12" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -667,11 +1362,9 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="23" customHeight="1">
+    <row r="10" spans="1:9" ht="12" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="16" t="s">
-        <v>11</v>
-      </c>
+      <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
@@ -680,7 +1373,7 @@
       <c r="H10" s="16"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" ht="23" customHeight="1">
+    <row r="11" spans="1:9" ht="12" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -691,168 +1384,168 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="26" customHeight="1">
+    <row r="12" spans="1:9" ht="32" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="23" customHeight="1">
+    <row r="13" spans="1:9" ht="30" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="24" t="s">
         <v>14</v>
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="23" customHeight="1">
+    <row r="14" spans="1:9" ht="29" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="4">
+      <c r="B14" s="37">
         <v>16.5</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="38">
         <v>548.31555951707924</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="4">
+      <c r="F14" s="37">
         <v>15</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="38">
         <v>531.39754389001621</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" ht="23" customHeight="1">
+    <row r="15" spans="1:9" ht="29" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="4">
+      <c r="B15" s="41">
         <v>17.5</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="42">
         <v>537.31555951707935</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="4">
+      <c r="F15" s="41">
         <v>17.5</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="42">
         <v>509.39754389001621</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="23" customHeight="1">
+    <row r="16" spans="1:9" ht="29" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="4">
+      <c r="B16" s="37">
         <v>20</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="38">
         <v>517.31555951707935</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="4">
+      <c r="F16" s="37">
         <v>20</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="38">
         <v>492.39754389001627</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" ht="23" customHeight="1">
+    <row r="17" spans="1:9" ht="29" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="4">
+      <c r="B17" s="41">
         <v>22.5</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="42">
         <v>500.31555951707929</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="4">
+      <c r="F17" s="41">
         <v>22.5</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="42">
         <v>479.39754389001627</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" ht="23" customHeight="1">
+    <row r="18" spans="1:9" ht="29" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="4">
+      <c r="B18" s="37">
         <v>25</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="38">
         <v>488.31555951707929</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="4">
+      <c r="F18" s="37">
         <v>25</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="38">
         <v>468.39754389001627</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" ht="23" customHeight="1">
+    <row r="19" spans="1:9" ht="29" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="4">
+      <c r="B19" s="41">
         <v>27.5</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="42">
         <v>477.31555951707929</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="1"/>
@@ -861,7 +1554,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" ht="23" customHeight="1">
+    <row r="20" spans="1:9" ht="12" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -872,7 +1565,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" ht="23" customHeight="1">
+    <row r="21" spans="1:9" ht="12" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -883,7 +1576,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" ht="23" customHeight="1">
+    <row r="22" spans="1:9" ht="12" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -894,183 +1587,183 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" ht="26" customHeight="1">
+    <row r="23" spans="1:9" ht="32" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" ht="23" customHeight="1">
+    <row r="24" spans="1:9" ht="30" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="24" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" ht="23" customHeight="1">
+    <row r="25" spans="1:9" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="4">
+      <c r="B25" s="37">
         <v>39</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="38">
         <v>331.93653951936574</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="4">
+      <c r="F25" s="37">
         <v>34</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="38">
         <v>341.18265644791148</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="39" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" ht="23" customHeight="1">
+    <row r="26" spans="1:9" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="4">
+      <c r="B26" s="41">
         <v>44</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="42">
         <v>322.93653951936574</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="4">
+      <c r="F26" s="41">
         <v>39</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="42">
         <v>332.18265644791143</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" ht="23" customHeight="1">
+    <row r="27" spans="1:9" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="4">
+      <c r="B27" s="37">
         <v>49</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="38">
         <v>316.93653951936574</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="4">
+      <c r="F27" s="37">
         <v>44</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="38">
         <v>325.18265644791143</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" ht="23" customHeight="1">
+    <row r="28" spans="1:9" ht="29" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="4">
+      <c r="B28" s="41">
         <v>54</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="42">
         <v>310.93653951936574</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="4">
+      <c r="F28" s="41">
         <v>49</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="42">
         <v>319.18265644791143</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" ht="23" customHeight="1">
+    <row r="29" spans="1:9" ht="29" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="4">
+      <c r="B29" s="37">
         <v>59</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="38">
         <v>306.93653951936579</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="4">
+      <c r="F29" s="37">
         <v>54</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="38">
         <v>315.18265644791143</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:9" ht="23" customHeight="1">
+    <row r="30" spans="1:9" ht="29" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="4">
+      <c r="B30" s="41">
         <v>64</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="42">
         <v>302.93653951936579</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="4">
+      <c r="F30" s="41">
         <v>59</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="42">
         <v>311.18265644791148</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" ht="23" customHeight="1">
+    <row r="31" spans="1:9" ht="12" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1081,7 +1774,7 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" ht="23" customHeight="1">
+    <row r="32" spans="1:9" ht="12" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1092,24 +1785,22 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" ht="23" customHeight="1">
+    <row r="33" spans="1:9" ht="24" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:9" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="13" t="s">
-        <v>20</v>
-      </c>
+      <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -1131,9 +1822,7 @@
     </row>
     <row r="36" spans="1:9" ht="23" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="13" t="s">
-        <v>21</v>
-      </c>
+      <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
@@ -1144,9 +1833,7 @@
     </row>
     <row r="37" spans="1:9" ht="23" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="13" t="s">
-        <v>34</v>
-      </c>
+      <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
@@ -1157,9 +1844,7 @@
     </row>
     <row r="38" spans="1:9" ht="23" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="13" t="s">
-        <v>22</v>
-      </c>
+      <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
@@ -1364,7 +2049,7 @@
     <col min="9" max="9" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23" customHeight="1">
+    <row r="1" spans="1:9" ht="12" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1375,33 +2060,35 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="32" customHeight="1">
+    <row r="2" spans="1:9" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="23" customHeight="1">
+    <row r="3" spans="1:9" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>黄色单元格为手动输入。</t>
+        </is>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="23" customHeight="1">
+    <row r="4" spans="1:9" ht="12" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1412,72 +2099,72 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="26" customHeight="1">
+    <row r="5" spans="1:9" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" ht="23" customHeight="1">
+    <row r="6" spans="1:9" ht="30" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="24" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="10">
+      <c r="G6" s="26"/>
+      <c r="H6" s="27">
         <v>2.5</v>
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" ht="23" customHeight="1">
+    <row r="7" spans="1:9" ht="29" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="29">
         <v>186</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="29">
         <v>188</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="11">
+      <c r="G7" s="31"/>
+      <c r="H7" s="32">
         <v>180</v>
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="23" customHeight="1">
+    <row r="8" spans="1:9" ht="29" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="34">
         <v>106</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="34">
         <v>109</v>
       </c>
       <c r="E8" s="1"/>
@@ -1486,7 +2173,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" ht="23" customHeight="1">
+    <row r="9" spans="1:9" ht="12" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1497,11 +2184,9 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="23" customHeight="1">
+    <row r="10" spans="1:9" ht="12" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="16" t="s">
-        <v>11</v>
-      </c>
+      <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
@@ -1510,7 +2195,7 @@
       <c r="H10" s="16"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" ht="23" customHeight="1">
+    <row r="11" spans="1:9" ht="12" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1521,168 +2206,168 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="26" customHeight="1">
+    <row r="12" spans="1:9" ht="32" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="23" customHeight="1">
+    <row r="13" spans="1:9" ht="30" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="24" t="s">
         <v>14</v>
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="23" customHeight="1">
+    <row r="14" spans="1:9" ht="29" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="4">
+      <c r="B14" s="37">
         <v>17.2</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="38">
         <v>565.31555951707924</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="4">
-        <v>16</v>
-      </c>
-      <c r="G14" s="12">
+      <c r="F14" s="37">
+        <v>16</v>
+      </c>
+      <c r="G14" s="38">
         <v>551.39754389001632</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" ht="23" customHeight="1">
+    <row r="15" spans="1:9" ht="29" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="4">
+      <c r="B15" s="41">
         <v>18.5</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="42">
         <v>554.31555951707924</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="4">
+      <c r="F15" s="41">
         <v>18.5</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="42">
         <v>530.39754389001621</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="23" customHeight="1">
+    <row r="16" spans="1:9" ht="29" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="4">
+      <c r="B16" s="37">
         <v>21</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="38">
         <v>534.31555951707924</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="4">
+      <c r="F16" s="37">
         <v>21</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="38">
         <v>515.39754389001621</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" ht="23" customHeight="1">
+    <row r="17" spans="1:9" ht="29" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="4">
+      <c r="B17" s="41">
         <v>23.5</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="42">
         <v>517.31555951707935</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="4">
+      <c r="F17" s="41">
         <v>23.5</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="42">
         <v>502.39754389001621</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" ht="23" customHeight="1">
+    <row r="18" spans="1:9" ht="29" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="4">
+      <c r="B18" s="37">
         <v>26</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="38">
         <v>505.31555951707929</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="4">
+      <c r="F18" s="37">
         <v>26</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="38">
         <v>492.39754389001627</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" ht="23" customHeight="1">
+    <row r="19" spans="1:9" ht="29" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="4">
+      <c r="B19" s="41">
         <v>28.5</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="42">
         <v>494.31555951707929</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="1"/>
@@ -1691,7 +2376,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" ht="23" customHeight="1">
+    <row r="20" spans="1:9" ht="12" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1702,7 +2387,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" ht="23" customHeight="1">
+    <row r="21" spans="1:9" ht="12" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1713,7 +2398,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" ht="23" customHeight="1">
+    <row r="22" spans="1:9" ht="12" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1724,183 +2409,183 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" ht="26" customHeight="1">
+    <row r="23" spans="1:9" ht="32" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" ht="23" customHeight="1">
+    <row r="24" spans="1:9" ht="30" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="24" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" ht="23" customHeight="1">
+    <row r="25" spans="1:9" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="4">
+      <c r="B25" s="37">
         <v>37.5</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="38">
         <v>339.93653951936574</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="4">
+      <c r="F25" s="37">
         <v>32.5</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="38">
         <v>341.18265644791148</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="39" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" ht="23" customHeight="1">
+    <row r="26" spans="1:9" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="4">
+      <c r="B26" s="41">
         <v>42.5</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="42">
         <v>329.93653951936574</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="4">
+      <c r="F26" s="41">
         <v>37.5</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="42">
         <v>331.18265644791143</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" ht="23" customHeight="1">
+    <row r="27" spans="1:9" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="4">
+      <c r="B27" s="37">
         <v>47.5</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="38">
         <v>322.93653951936574</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="4">
+      <c r="F27" s="37">
         <v>42.5</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="38">
         <v>323.18265644791143</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" ht="23" customHeight="1">
+    <row r="28" spans="1:9" ht="29" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="4">
+      <c r="B28" s="41">
         <v>52.5</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="42">
         <v>315.93653951936574</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="4">
+      <c r="F28" s="41">
         <v>47.5</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="42">
         <v>318.18265644791143</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" ht="23" customHeight="1">
+    <row r="29" spans="1:9" ht="29" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="4">
+      <c r="B29" s="37">
         <v>57.5</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="38">
         <v>310.93653951936574</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="4">
+      <c r="F29" s="37">
         <v>52.5</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="38">
         <v>313.18265644791143</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:9" ht="23" customHeight="1">
+    <row r="30" spans="1:9" ht="29" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="4">
+      <c r="B30" s="41">
         <v>62.5</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="42">
         <v>306.93653951936579</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="4">
+      <c r="F30" s="41">
         <v>57.5</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="42">
         <v>310.18265644791148</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" ht="23" customHeight="1">
+    <row r="31" spans="1:9" ht="12" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1911,7 +2596,7 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" ht="23" customHeight="1">
+    <row r="32" spans="1:9" ht="12" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1922,24 +2607,22 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" ht="23" customHeight="1">
+    <row r="33" spans="1:9" ht="24" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:9" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="13" t="s">
-        <v>20</v>
-      </c>
+      <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -1961,9 +2644,7 @@
     </row>
     <row r="36" spans="1:9" ht="23" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="13" t="s">
-        <v>21</v>
-      </c>
+      <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
@@ -1974,9 +2655,7 @@
     </row>
     <row r="37" spans="1:9" ht="23" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="13" t="s">
-        <v>34</v>
-      </c>
+      <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
@@ -1987,9 +2666,7 @@
     </row>
     <row r="38" spans="1:9" ht="23" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="13" t="s">
-        <v>22</v>
-      </c>
+      <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
@@ -2194,7 +2871,7 @@
     <col min="9" max="9" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23" customHeight="1">
+    <row r="1" spans="1:9" ht="12" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2205,33 +2882,35 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="32" customHeight="1">
+    <row r="2" spans="1:9" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="23" customHeight="1">
+    <row r="3" spans="1:9" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>黄色单元格为手动输入。</t>
+        </is>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="23" customHeight="1">
+    <row r="4" spans="1:9" ht="12" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2242,79 +2921,79 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="26" customHeight="1">
+    <row r="5" spans="1:9" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" ht="23" customHeight="1">
+    <row r="6" spans="1:9" ht="30" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="24" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="10">
+      <c r="G6" s="26"/>
+      <c r="H6" s="27">
         <v>8</v>
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" ht="23" customHeight="1">
+    <row r="7" spans="1:9" ht="29" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="29">
         <v>123</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="29">
         <v>129</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="11">
+      <c r="G7" s="31"/>
+      <c r="H7" s="32">
         <v>180</v>
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="23" customHeight="1">
+    <row r="8" spans="1:9" ht="29" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="34">
         <v>114</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="46"/>
       <c r="E8" s="1"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" ht="23" customHeight="1">
+    <row r="9" spans="1:9" ht="12" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2325,20 +3004,22 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="23" customHeight="1">
+    <row r="10" spans="1:9" ht="24" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>RX3 后车高测点待确认。</t>
+        </is>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" ht="23" customHeight="1">
+    <row r="11" spans="1:9" ht="12" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2349,147 +3030,147 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="26" customHeight="1">
+    <row r="12" spans="1:9" ht="32" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="23" customHeight="1">
+    <row r="13" spans="1:9" ht="30" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="24" t="s">
         <v>14</v>
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="23" customHeight="1">
+    <row r="14" spans="1:9" ht="29" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="4">
+      <c r="B14" s="37">
         <v>28.5</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="38">
         <v>447.31555951707924</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="4">
+      <c r="F14" s="37">
         <v>24.5</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="38">
         <v>456.39754389001627</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" ht="23" customHeight="1">
+    <row r="15" spans="1:9" ht="29" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="4">
+      <c r="B15" s="41">
         <v>32.5</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="42">
         <v>438.31555951707929</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="4">
+      <c r="F15" s="41">
         <v>28.5</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="42">
         <v>444.39754389001627</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="23" customHeight="1">
+    <row r="16" spans="1:9" ht="29" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="4">
+      <c r="B16" s="37">
         <v>36.5</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="38">
         <v>430.31555951707929</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="4">
+      <c r="F16" s="37">
         <v>32.5</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="38">
         <v>436.39754389001627</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" ht="23" customHeight="1">
+    <row r="17" spans="1:9" ht="29" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="47"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="47"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" ht="23" customHeight="1">
+    <row r="18" spans="1:9" ht="29" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="49"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="49"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" ht="23" customHeight="1">
+    <row r="19" spans="1:9" ht="29" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="47"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="12"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" ht="23" customHeight="1">
+    <row r="20" spans="1:9" ht="12" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2500,7 +3181,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" ht="23" customHeight="1">
+    <row r="21" spans="1:9" ht="12" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2511,7 +3192,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" ht="23" customHeight="1">
+    <row r="22" spans="1:9" ht="12" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2522,123 +3203,123 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" ht="26" customHeight="1">
+    <row r="23" spans="1:9" ht="32" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" ht="23" customHeight="1">
+    <row r="24" spans="1:9" ht="30" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="24" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" ht="23" customHeight="1">
+    <row r="25" spans="1:9" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="4">
+      <c r="B25" s="37">
         <v>36</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="38">
         <v>285.93653951936574</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="4">
+      <c r="F25" s="37">
         <v>33</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="38">
         <v>332.18265644791143</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="40" t="s">
         <v>16</v>
       </c>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" ht="23" customHeight="1">
+    <row r="26" spans="1:9" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="47"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="47"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" ht="23" customHeight="1">
+    <row r="27" spans="1:9" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="49"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="49"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" ht="23" customHeight="1">
+    <row r="28" spans="1:9" ht="29" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="47"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="47"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" ht="23" customHeight="1">
+    <row r="29" spans="1:9" ht="29" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="49"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="49"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:9" ht="23" customHeight="1">
+    <row r="30" spans="1:9" ht="29" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="47"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="47"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" ht="23" customHeight="1">
+    <row r="31" spans="1:9" ht="12" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2649,7 +3330,7 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" ht="23" customHeight="1">
+    <row r="32" spans="1:9" ht="12" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2660,24 +3341,22 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" ht="23" customHeight="1">
+    <row r="33" spans="1:9" ht="24" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:9" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="13" t="s">
-        <v>20</v>
-      </c>
+      <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -2699,9 +3378,7 @@
     </row>
     <row r="36" spans="1:9" ht="23" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="13" t="s">
-        <v>21</v>
-      </c>
+      <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
@@ -2712,9 +3389,7 @@
     </row>
     <row r="37" spans="1:9" ht="23" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="13" t="s">
-        <v>34</v>
-      </c>
+      <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
@@ -2725,9 +3400,7 @@
     </row>
     <row r="38" spans="1:9" ht="23" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="13" t="s">
-        <v>33</v>
-      </c>
+      <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>

--- a/docs/springs_RH.xlsx
+++ b/docs/springs_RH.xlsx
@@ -1322,7 +1322,7 @@
         <v>186</v>
       </c>
       <c r="D7" s="29">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="30" t="s">
@@ -2141,7 +2141,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="29">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D7" s="29">
         <v>188</v>

--- a/docs/springs_RH.xlsx
+++ b/docs/springs_RH.xlsx
@@ -128,10 +128,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="0"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="81">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -372,8 +375,275 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF283C50"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="76">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,8 +820,204 @@
         <fgColor rgb="FFF5F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -827,11 +1293,287 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="33"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -944,6 +1686,187 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="33" xfId="1"/>
+    <xf numFmtId="0" fontId="42" fillId="40" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="38" borderId="33" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="39" borderId="33" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="39" borderId="33" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="39" borderId="33" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="38" fillId="38" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="45" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="50" fillId="48" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="49" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="52" fillId="50" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="55" fillId="53" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="54" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="57" fillId="55" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="60" fillId="58" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="61" fillId="59" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="60" borderId="54" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="55" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="64" fillId="62" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="65" fillId="63" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="64" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="69" fillId="67" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="68" borderId="62" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="71" fillId="69" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="70" borderId="64" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="73" fillId="71" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="41" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="42" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="43" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="44" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="46" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="47" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="39" borderId="33" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="52" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="65" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="66" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="56" borderId="50" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="57" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="38" borderId="33" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="36" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="36" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="72" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="72" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="73" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="73" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="73" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="74" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="74" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="74" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="75" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="75" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="75" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="75" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="75" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="74" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="73" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="74" fillId="74" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="74" fillId="73" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="74" fillId="73" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="74" fillId="74" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="36" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="36" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1583,7 +2506,7 @@
         <v>34</v>
       </c>
       <c r="G25" s="15">
-        <v>341.18265644791148</v>
+        <v>344.1826564479115</v>
       </c>
       <c r="H25" s="16" t="s">
         <v>13</v>
@@ -1606,7 +2529,7 @@
         <v>39</v>
       </c>
       <c r="G26" s="19">
-        <v>332.18265644791143</v>
+        <v>335.1826564479114</v>
       </c>
       <c r="H26" s="20" t="s">
         <v>14</v>
@@ -1629,7 +2552,7 @@
         <v>44</v>
       </c>
       <c r="G27" s="15">
-        <v>325.18265644791143</v>
+        <v>328.1826564479114</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>14</v>
@@ -1652,7 +2575,7 @@
         <v>49</v>
       </c>
       <c r="G28" s="19">
-        <v>319.18265644791143</v>
+        <v>322.1826564479114</v>
       </c>
       <c r="H28" s="20" t="s">
         <v>14</v>
@@ -1675,7 +2598,7 @@
         <v>54</v>
       </c>
       <c r="G29" s="15">
-        <v>315.18265644791143</v>
+        <v>318.1826564479114</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>14</v>
@@ -1698,7 +2621,7 @@
         <v>59</v>
       </c>
       <c r="G30" s="19">
-        <v>311.18265644791148</v>
+        <v>314.1826564479114</v>
       </c>
       <c r="H30" s="20" t="s">
         <v>14</v>
@@ -1751,126 +2674,184 @@
       <c r="H34" s="32"/>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A35" s="2"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A36" s="2"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A37" s="2"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A38" s="2"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A41" s="2"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A43" s="2"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A45" s="2"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="2"/>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="42"/>
+      <c r="B35" s="83" t="str">
+        <v>Weight distribution · 重量分布</v>
+      </c>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="42"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="42"/>
+      <c r="B36" s="94" t="str">
+        <v>项目</v>
+      </c>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="93" t="str">
+        <v>Gravel</v>
+      </c>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93" t="str">
+        <v>Tarmac</v>
+      </c>
+      <c r="H36" s="93"/>
+      <c r="I36" s="42"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="42"/>
+      <c r="B37" s="95" t="str">
+        <v>整车总重 (kg)</v>
+      </c>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="97" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F37" s="97"/>
+      <c r="G37" s="97" t="n">
+        <v>1390</v>
+      </c>
+      <c r="H37" s="97"/>
+      <c r="I37" s="42"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="42"/>
+      <c r="B38" s="96" t="str">
+        <v>FL · 左前 (kg)</v>
+      </c>
+      <c r="C38" s="96"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="98" t="n">
+        <v>371</v>
+      </c>
+      <c r="F38" s="98"/>
+      <c r="G38" s="98" t="n">
+        <v>370</v>
+      </c>
+      <c r="H38" s="98"/>
+      <c r="I38" s="42"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="42"/>
+      <c r="B39" s="95" t="str">
+        <v>FR · 右前 (kg)</v>
+      </c>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="97" t="n">
+        <v>370</v>
+      </c>
+      <c r="F39" s="97"/>
+      <c r="G39" s="97" t="n">
+        <v>370</v>
+      </c>
+      <c r="H39" s="97"/>
+      <c r="I39" s="42"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="42"/>
+      <c r="B40" s="96" t="str">
+        <v>RL · 左后 (kg)</v>
+      </c>
+      <c r="C40" s="96"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="98" t="n">
+        <v>324</v>
+      </c>
+      <c r="F40" s="98"/>
+      <c r="G40" s="98" t="n">
+        <v>326</v>
+      </c>
+      <c r="H40" s="98"/>
+      <c r="I40" s="42"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="42"/>
+      <c r="B41" s="95" t="str">
+        <v>RR · 右后 (kg)</v>
+      </c>
+      <c r="C41" s="95"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="97" t="n">
+        <v>325</v>
+      </c>
+      <c r="F41" s="97"/>
+      <c r="G41" s="97" t="n">
+        <v>325</v>
+      </c>
+      <c r="H41" s="97"/>
+      <c r="I41" s="42"/>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="42"/>
+      <c r="B42" s="96" t="str">
+        <v>前轴占比</v>
+      </c>
+      <c r="C42" s="96"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="99" t="n">
+        <f>SUM(E38:E39)/SUM(E38:E41)</f>
+        <v>0.5330935251798561</v>
+      </c>
+      <c r="F42" s="99"/>
+      <c r="G42" s="99" t="n">
+        <f>SUM(G38:G39)/SUM(G38:G41)</f>
+        <v>0.5319913731128685</v>
+      </c>
+      <c r="H42" s="99"/>
+      <c r="I42" s="42"/>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="42"/>
+      <c r="B43" s="95" t="str">
+        <v>后轴占比</v>
+      </c>
+      <c r="C43" s="95"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="100" t="n">
+        <f>SUM(E40:E41)/SUM(E38:E41)</f>
+        <v>0.46690647482014386</v>
+      </c>
+      <c r="F43" s="100"/>
+      <c r="G43" s="100" t="n">
+        <f>SUM(G40:G41)/SUM(G38:G41)</f>
+        <v>0.4680086268871316</v>
+      </c>
+      <c r="H43" s="100"/>
+      <c r="I43" s="42"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="42"/>
+      <c r="B44" s="101" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="C44" s="101"/>
+      <c r="D44" s="101"/>
+      <c r="E44" s="101"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="101"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="42"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="42"/>
+      <c r="B45" s="102" t="str">
+        <v>轮荷为 UI 近似读数；前后比例按四轮读数计算。</v>
+      </c>
+      <c r="C45" s="102"/>
+      <c r="D45" s="102"/>
+      <c r="E45" s="102"/>
+      <c r="F45" s="102"/>
+      <c r="G45" s="102"/>
+      <c r="H45" s="102"/>
+      <c r="I45" s="42"/>
     </row>
     <row r="46" spans="1:9" ht="23.1" customHeight="1">
       <c r="A46" s="2"/>
@@ -1950,16 +2931,10 @@
       <c r="I52" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B42:H42"/>
+  <mergeCells count="40">
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="F12:H12"/>
@@ -1970,6 +2945,33 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B45:H45"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2393,7 +3395,7 @@
         <v>37.5</v>
       </c>
       <c r="C25" s="15">
-        <v>339.93653951936574</v>
+        <v>345.93653951936574</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>13</v>
@@ -2403,7 +3405,7 @@
         <v>32.5</v>
       </c>
       <c r="G25" s="15">
-        <v>341.18265644791148</v>
+        <v>347.1826564479115</v>
       </c>
       <c r="H25" s="16" t="s">
         <v>13</v>
@@ -2416,7 +3418,7 @@
         <v>42.5</v>
       </c>
       <c r="C26" s="19">
-        <v>329.93653951936574</v>
+        <v>335.93653951936574</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>14</v>
@@ -2426,7 +3428,7 @@
         <v>37.5</v>
       </c>
       <c r="G26" s="19">
-        <v>331.18265644791143</v>
+        <v>337.1826564479114</v>
       </c>
       <c r="H26" s="20" t="s">
         <v>14</v>
@@ -2439,7 +3441,7 @@
         <v>47.5</v>
       </c>
       <c r="C27" s="15">
-        <v>322.93653951936574</v>
+        <v>328.93653951936574</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>14</v>
@@ -2449,7 +3451,7 @@
         <v>42.5</v>
       </c>
       <c r="G27" s="15">
-        <v>323.18265644791143</v>
+        <v>329.1826564479114</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>14</v>
@@ -2462,7 +3464,7 @@
         <v>52.5</v>
       </c>
       <c r="C28" s="19">
-        <v>315.93653951936574</v>
+        <v>321.93653951936574</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>14</v>
@@ -2472,7 +3474,7 @@
         <v>47.5</v>
       </c>
       <c r="G28" s="19">
-        <v>318.18265644791143</v>
+        <v>324.1826564479114</v>
       </c>
       <c r="H28" s="20" t="s">
         <v>14</v>
@@ -2485,7 +3487,7 @@
         <v>57.5</v>
       </c>
       <c r="C29" s="15">
-        <v>310.93653951936574</v>
+        <v>316.93653951936574</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>14</v>
@@ -2495,7 +3497,7 @@
         <v>52.5</v>
       </c>
       <c r="G29" s="15">
-        <v>313.18265644791143</v>
+        <v>319.1826564479114</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>14</v>
@@ -2508,7 +3510,7 @@
         <v>62.5</v>
       </c>
       <c r="C30" s="19">
-        <v>306.93653951936579</v>
+        <v>312.93653951936574</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>14</v>
@@ -2518,7 +3520,7 @@
         <v>57.5</v>
       </c>
       <c r="G30" s="19">
-        <v>310.18265644791148</v>
+        <v>316.1826564479114</v>
       </c>
       <c r="H30" s="20" t="s">
         <v>14</v>
@@ -2571,126 +3573,184 @@
       <c r="H34" s="32"/>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A35" s="2"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A36" s="2"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A37" s="2"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A38" s="2"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A41" s="2"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A43" s="2"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A45" s="2"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="2"/>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="42"/>
+      <c r="B35" s="83" t="str">
+        <v>Weight distribution · 重量分布</v>
+      </c>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="42"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="42"/>
+      <c r="B36" s="94" t="str">
+        <v>项目</v>
+      </c>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="93" t="str">
+        <v>Gravel</v>
+      </c>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93" t="str">
+        <v>Tarmac</v>
+      </c>
+      <c r="H36" s="93"/>
+      <c r="I36" s="42"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="42"/>
+      <c r="B37" s="95" t="str">
+        <v>整车总重 (kg)</v>
+      </c>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="97" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F37" s="97"/>
+      <c r="G37" s="97" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H37" s="97"/>
+      <c r="I37" s="42"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="42"/>
+      <c r="B38" s="96" t="str">
+        <v>FL · 左前 (kg)</v>
+      </c>
+      <c r="C38" s="96"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="98" t="n">
+        <v>389</v>
+      </c>
+      <c r="F38" s="98"/>
+      <c r="G38" s="98" t="n">
+        <v>388</v>
+      </c>
+      <c r="H38" s="98"/>
+      <c r="I38" s="42"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="42"/>
+      <c r="B39" s="95" t="str">
+        <v>FR · 右前 (kg)</v>
+      </c>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="97" t="n">
+        <v>388</v>
+      </c>
+      <c r="F39" s="97"/>
+      <c r="G39" s="97" t="n">
+        <v>388</v>
+      </c>
+      <c r="H39" s="97"/>
+      <c r="I39" s="42"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="42"/>
+      <c r="B40" s="96" t="str">
+        <v>RL · 左后 (kg)</v>
+      </c>
+      <c r="C40" s="96"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="98" t="n">
+        <v>322</v>
+      </c>
+      <c r="F40" s="98"/>
+      <c r="G40" s="98" t="n">
+        <v>322</v>
+      </c>
+      <c r="H40" s="98"/>
+      <c r="I40" s="42"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="42"/>
+      <c r="B41" s="95" t="str">
+        <v>RR · 右后 (kg)</v>
+      </c>
+      <c r="C41" s="95"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="97" t="n">
+        <v>321</v>
+      </c>
+      <c r="F41" s="97"/>
+      <c r="G41" s="97" t="n">
+        <v>322</v>
+      </c>
+      <c r="H41" s="97"/>
+      <c r="I41" s="42"/>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="42"/>
+      <c r="B42" s="96" t="str">
+        <v>前轴占比</v>
+      </c>
+      <c r="C42" s="96"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="99" t="n">
+        <f>SUM(E38:E39)/SUM(E38:E41)</f>
+        <v>0.5471830985915493</v>
+      </c>
+      <c r="F42" s="99"/>
+      <c r="G42" s="99" t="n">
+        <f>SUM(G38:G39)/SUM(G38:G41)</f>
+        <v>0.5464788732394367</v>
+      </c>
+      <c r="H42" s="99"/>
+      <c r="I42" s="42"/>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="42"/>
+      <c r="B43" s="95" t="str">
+        <v>后轴占比</v>
+      </c>
+      <c r="C43" s="95"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="100" t="n">
+        <f>SUM(E40:E41)/SUM(E38:E41)</f>
+        <v>0.4528169014084507</v>
+      </c>
+      <c r="F43" s="100"/>
+      <c r="G43" s="100" t="n">
+        <f>SUM(G40:G41)/SUM(G38:G41)</f>
+        <v>0.4535211267605634</v>
+      </c>
+      <c r="H43" s="100"/>
+      <c r="I43" s="42"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="42"/>
+      <c r="B44" s="101" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="C44" s="101"/>
+      <c r="D44" s="101"/>
+      <c r="E44" s="101"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="101"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="42"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="42"/>
+      <c r="B45" s="102" t="str">
+        <v>轮荷为 UI 近似读数；前后比例按四轮读数计算。</v>
+      </c>
+      <c r="C45" s="102"/>
+      <c r="D45" s="102"/>
+      <c r="E45" s="102"/>
+      <c r="F45" s="102"/>
+      <c r="G45" s="102"/>
+      <c r="H45" s="102"/>
+      <c r="I45" s="42"/>
     </row>
     <row r="46" spans="1:9" ht="23.1" customHeight="1">
       <c r="A46" s="2"/>
@@ -2770,16 +3830,10 @@
       <c r="I52" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B42:H42"/>
+  <mergeCells count="40">
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="F12:H12"/>
@@ -2790,6 +3844,33 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B45:H45"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
